--- a/2022 data/excel_outputs/99_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/99_boothwise_data.xlsx
@@ -14,11 +14,80 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="445">
   <si>
     <t>AC 99 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -391,7 +460,7 @@
     <t>P.S.URAVAR HASTRAF R.N. 1</t>
   </si>
   <si>
-    <t>P.S.URAVAR HASTRAF R.N. ■</t>
+    <t>PRA0PA0 MAHAKEPURA</t>
   </si>
   <si>
     <t>J.H.S.URAWAR HASTRAPH R.N.1</t>
@@ -661,7 +730,7 @@
     <t>P.S. JARAILA</t>
   </si>
   <si>
-    <t>MOOLCHAND J.H.NANDPUR R.N. ■</t>
+    <t>KSHE0I0KA0 SIRASAGAMJ K0N01</t>
   </si>
   <si>
     <t>MOOLCHAND J.H.NANDPUR R.N. 2</t>
@@ -757,7 +826,7 @@
     <t>JANSHAKTI J.H.S.KARHARA R.N.2</t>
   </si>
   <si>
-    <t>P.S.NAGLA KHUSHALI R.N. ■</t>
+    <t>JU0HA0 SIMGEMARI K0N02</t>
   </si>
   <si>
     <t>P.S.NAGLA KHUSHALI R.N. 2</t>
@@ -1286,8 +1355,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1303,7 +1380,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1311,12 +1388,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1615,82 +1710,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="D2" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="E2" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="F2" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="G2" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="H2" t="s">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="I2" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="J2" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="K2" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="L2" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="M2" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="N2" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="O2" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="P2" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="Q2" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="R2" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="S2" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="T2" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="U2" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="V2" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="W2" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="X2" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1698,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1028</v>
@@ -1772,7 +1936,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>1030</v>
@@ -1846,7 +2010,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>1174</v>
@@ -1920,7 +2084,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>538</v>
@@ -1994,7 +2158,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>1067</v>
@@ -2068,7 +2232,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>671</v>
@@ -2142,7 +2306,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>686</v>
@@ -2216,7 +2380,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>1095</v>
@@ -2290,7 +2454,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>913</v>
@@ -2364,7 +2528,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>484</v>
@@ -2438,7 +2602,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>615</v>
@@ -2512,7 +2676,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>621</v>
@@ -2586,7 +2750,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>575</v>
@@ -2660,7 +2824,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>984</v>
@@ -2734,7 +2898,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>1187</v>
@@ -2808,7 +2972,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>703</v>
@@ -2882,7 +3046,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>772</v>
@@ -2956,7 +3120,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>626</v>
@@ -3030,7 +3194,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>816</v>
@@ -3104,7 +3268,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>778</v>
@@ -3178,7 +3342,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>947</v>
@@ -3252,7 +3416,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>962</v>
@@ -3326,7 +3490,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>982</v>
@@ -3400,7 +3564,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>854</v>
@@ -3474,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>676</v>
@@ -3548,7 +3712,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>716</v>
@@ -3622,7 +3786,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>624</v>
@@ -3696,7 +3860,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>619</v>
@@ -3770,7 +3934,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>1140</v>
@@ -3844,7 +4008,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>1075</v>
@@ -3918,7 +4082,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>653</v>
@@ -3992,7 +4156,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>537</v>
@@ -4066,7 +4230,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>733</v>
@@ -4140,7 +4304,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>809</v>
@@ -4214,7 +4378,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -4288,7 +4452,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>527</v>
@@ -4362,7 +4526,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>896</v>
@@ -4436,7 +4600,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>1043</v>
@@ -4510,7 +4674,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>585</v>
@@ -4584,7 +4748,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>701</v>
@@ -4658,7 +4822,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>660</v>
@@ -4732,7 +4896,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>371</v>
@@ -4806,7 +4970,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>679</v>
@@ -4880,7 +5044,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>727</v>
@@ -4954,7 +5118,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>588</v>
@@ -5028,7 +5192,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>730</v>
@@ -5102,7 +5266,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>723</v>
@@ -5176,7 +5340,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>1029</v>
@@ -5250,7 +5414,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>605</v>
@@ -5324,7 +5488,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>590</v>
@@ -5398,7 +5562,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>1159</v>
@@ -5472,7 +5636,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>622</v>
@@ -5546,7 +5710,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>746</v>
@@ -5620,7 +5784,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>403</v>
@@ -5694,7 +5858,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>1036</v>
@@ -5768,7 +5932,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>905</v>
@@ -5842,7 +6006,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>593</v>
@@ -5916,7 +6080,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>395</v>
@@ -5990,7 +6154,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>901</v>
@@ -6064,7 +6228,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>786</v>
@@ -6138,7 +6302,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>834</v>
@@ -6212,7 +6376,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>863</v>
@@ -6286,7 +6450,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>1070</v>
@@ -6360,7 +6524,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>626</v>
@@ -6434,7 +6598,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>1113</v>
@@ -6508,7 +6672,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>353</v>
@@ -6582,7 +6746,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>553</v>
@@ -6656,7 +6820,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>709</v>
@@ -6730,7 +6894,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>553</v>
@@ -6804,7 +6968,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>665</v>
@@ -6878,7 +7042,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>647</v>
@@ -6952,7 +7116,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>399</v>
@@ -7026,7 +7190,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>861</v>
@@ -7100,7 +7264,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>857</v>
@@ -7174,7 +7338,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>943</v>
@@ -7248,7 +7412,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>1004</v>
@@ -7322,7 +7486,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>855</v>
@@ -7396,7 +7560,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>909</v>
@@ -7470,7 +7634,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -7544,7 +7708,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>774</v>
@@ -7618,7 +7782,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>752</v>
@@ -7692,7 +7856,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>1053</v>
@@ -7766,7 +7930,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>959</v>
@@ -7840,7 +8004,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>456</v>
@@ -7914,7 +8078,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>744</v>
@@ -7988,7 +8152,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>643</v>
@@ -8062,7 +8226,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>1035</v>
@@ -8136,7 +8300,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>746</v>
@@ -8210,7 +8374,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>571</v>
@@ -8284,7 +8448,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>811</v>
@@ -8358,7 +8522,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>1160</v>
@@ -8432,7 +8596,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>1105</v>
@@ -8506,7 +8670,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>820</v>
@@ -8580,7 +8744,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>1018</v>
@@ -8654,7 +8818,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>939</v>
@@ -8728,7 +8892,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>1030</v>
@@ -8802,7 +8966,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>453</v>
@@ -8876,7 +9040,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>1032</v>
@@ -8950,7 +9114,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>976</v>
@@ -9024,7 +9188,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>1110</v>
@@ -9098,7 +9262,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>669</v>
@@ -9172,7 +9336,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>675</v>
@@ -9246,7 +9410,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>971</v>
@@ -9320,7 +9484,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>1022</v>
@@ -9394,7 +9558,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>782</v>
@@ -9468,7 +9632,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>1072</v>
@@ -9542,7 +9706,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>1121</v>
@@ -9616,7 +9780,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>978</v>
@@ -9690,7 +9854,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>741</v>
@@ -9764,7 +9928,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>675</v>
@@ -9838,7 +10002,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>1039</v>
@@ -9912,7 +10076,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>892</v>
@@ -9986,7 +10150,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>750</v>
@@ -10060,7 +10224,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>1001</v>
@@ -10134,7 +10298,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>838</v>
@@ -10208,7 +10372,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>826</v>
@@ -10282,7 +10446,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>836</v>
@@ -10356,7 +10520,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>841</v>
@@ -10430,7 +10594,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>1165</v>
@@ -10504,7 +10668,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>894</v>
@@ -10578,7 +10742,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>953</v>
@@ -10652,7 +10816,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>716</v>
@@ -10726,7 +10890,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>686</v>
@@ -10800,7 +10964,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>955</v>
@@ -10874,7 +11038,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>1024</v>
@@ -10948,7 +11112,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>487</v>
@@ -11022,7 +11186,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>1018</v>
@@ -11096,7 +11260,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>627</v>
@@ -11170,7 +11334,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>1118</v>
@@ -11244,7 +11408,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>1090</v>
@@ -11318,7 +11482,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>442</v>
@@ -11392,7 +11556,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>804</v>
@@ -11466,7 +11630,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>818</v>
@@ -11540,7 +11704,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>1194</v>
@@ -11614,7 +11778,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>737</v>
@@ -11688,7 +11852,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>829</v>
@@ -11762,7 +11926,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>733</v>
@@ -11836,7 +12000,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>626</v>
@@ -11910,7 +12074,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>587</v>
@@ -11984,7 +12148,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>562</v>
@@ -12058,7 +12222,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="C143">
         <v>763</v>
@@ -12132,7 +12296,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>706</v>
@@ -12206,7 +12370,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="C145">
         <v>623</v>
@@ -12280,7 +12444,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="C146">
         <v>587</v>
@@ -12354,7 +12518,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="C147">
         <v>1177</v>
@@ -12428,7 +12592,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C148">
         <v>572</v>
@@ -12502,7 +12666,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="C149">
         <v>827</v>
@@ -12576,7 +12740,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="C150">
         <v>611</v>
@@ -12650,7 +12814,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="C151">
         <v>616</v>
@@ -12724,7 +12888,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C152">
         <v>924</v>
@@ -12798,7 +12962,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C153">
         <v>751</v>
@@ -12872,7 +13036,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C154">
         <v>933</v>
@@ -12946,7 +13110,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C155">
         <v>937</v>
@@ -13020,7 +13184,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C156">
         <v>809</v>
@@ -13094,7 +13258,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C157">
         <v>814</v>
@@ -13168,7 +13332,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C158">
         <v>729</v>
@@ -13242,7 +13406,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C159">
         <v>1056</v>
@@ -13316,7 +13480,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C160">
         <v>947</v>
@@ -13390,7 +13554,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C161">
         <v>823</v>
@@ -13464,7 +13628,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C162">
         <v>622</v>
@@ -13538,7 +13702,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C163">
         <v>636</v>
@@ -13612,7 +13776,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="C164">
         <v>593</v>
@@ -13686,7 +13850,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C165">
         <v>809</v>
@@ -13760,7 +13924,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C166">
         <v>996</v>
@@ -13834,7 +13998,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C167">
         <v>500</v>
@@ -13908,7 +14072,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C168">
         <v>646</v>
@@ -13982,7 +14146,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C169">
         <v>653</v>
@@ -14056,7 +14220,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C170">
         <v>878</v>
@@ -14130,7 +14294,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C171">
         <v>1192</v>
@@ -14204,7 +14368,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C172">
         <v>740</v>
@@ -14278,7 +14442,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C173">
         <v>810</v>
@@ -14352,7 +14516,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C174">
         <v>401</v>
@@ -14426,7 +14590,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="C175">
         <v>1062</v>
@@ -14500,7 +14664,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="C176">
         <v>460</v>
@@ -14574,7 +14738,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C177">
         <v>446</v>
@@ -14648,7 +14812,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C178">
         <v>708</v>
@@ -14722,7 +14886,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="C179">
         <v>706</v>
@@ -14796,7 +14960,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C180">
         <v>801</v>
@@ -14870,7 +15034,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C181">
         <v>840</v>
@@ -14944,7 +15108,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C182">
         <v>720</v>
@@ -15018,7 +15182,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="C183">
         <v>753</v>
@@ -15092,7 +15256,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C184">
         <v>407</v>
@@ -15166,7 +15330,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C185">
         <v>707</v>
@@ -15240,7 +15404,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C186">
         <v>856</v>
@@ -15314,7 +15478,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C187">
         <v>614</v>
@@ -15388,7 +15552,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C188">
         <v>1034</v>
@@ -15462,7 +15626,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C189">
         <v>698</v>
@@ -15536,7 +15700,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C190">
         <v>554</v>
@@ -15610,7 +15774,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="C191">
         <v>1061</v>
@@ -15684,7 +15848,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C192">
         <v>707</v>
@@ -15758,7 +15922,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C193">
         <v>688</v>
@@ -15832,7 +15996,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C194">
         <v>1097</v>
@@ -15906,7 +16070,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="C195">
         <v>717</v>
@@ -15980,7 +16144,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C196">
         <v>698</v>
@@ -16054,7 +16218,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C197">
         <v>1171</v>
@@ -16128,7 +16292,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C198">
         <v>635</v>
@@ -16202,7 +16366,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C199">
         <v>649</v>
@@ -16276,7 +16440,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="C200">
         <v>874</v>
@@ -16350,7 +16514,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C201">
         <v>615</v>
@@ -16424,7 +16588,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C202">
         <v>482</v>
@@ -16498,7 +16662,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C203">
         <v>460</v>
@@ -16572,7 +16736,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C204">
         <v>943</v>
@@ -16646,7 +16810,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C205">
         <v>1010</v>
@@ -16720,7 +16884,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C206">
         <v>748</v>
@@ -16794,7 +16958,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C207">
         <v>772</v>
@@ -16868,7 +17032,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C208">
         <v>897</v>
@@ -16942,7 +17106,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="C209">
         <v>786</v>
@@ -17016,7 +17180,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C210">
         <v>855</v>
@@ -17090,7 +17254,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="C211">
         <v>697</v>
@@ -17164,7 +17328,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C212">
         <v>1099</v>
@@ -17238,7 +17402,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="C213">
         <v>1131</v>
@@ -17312,7 +17476,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="C214">
         <v>973</v>
@@ -17386,7 +17550,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="C215">
         <v>723</v>
@@ -17460,7 +17624,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C216">
         <v>667</v>
@@ -17534,7 +17698,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C217">
         <v>699</v>
@@ -17608,7 +17772,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="C218">
         <v>638</v>
@@ -17682,7 +17846,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C219">
         <v>1021</v>
@@ -17756,7 +17920,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C220">
         <v>1129</v>
@@ -17830,7 +17994,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C221">
         <v>762</v>
@@ -17904,7 +18068,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="C222">
         <v>1043</v>
@@ -17978,7 +18142,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C223">
         <v>927</v>
@@ -18052,7 +18216,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="C224">
         <v>367</v>
@@ -18126,7 +18290,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="C225">
         <v>952</v>
@@ -18200,7 +18364,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C226">
         <v>1058</v>
@@ -18274,7 +18438,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="C227">
         <v>805</v>
@@ -18348,7 +18512,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C228">
         <v>659</v>
@@ -18422,7 +18586,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C229">
         <v>667</v>
@@ -18496,7 +18660,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="C230">
         <v>1162</v>
@@ -18570,7 +18734,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C231">
         <v>1119</v>
@@ -18644,7 +18808,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C232">
         <v>716</v>
@@ -18718,7 +18882,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="C233">
         <v>656</v>
@@ -18792,7 +18956,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C234">
         <v>638</v>
@@ -18866,7 +19030,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C235">
         <v>756</v>
@@ -18940,7 +19104,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="C236">
         <v>1041</v>
@@ -19014,7 +19178,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="C237">
         <v>682</v>
@@ -19088,7 +19252,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C238">
         <v>837</v>
@@ -19162,7 +19326,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C239">
         <v>805</v>
@@ -19236,7 +19400,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="C240">
         <v>496</v>
@@ -19310,7 +19474,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C241">
         <v>500</v>
@@ -19384,7 +19548,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="C242">
         <v>679</v>
@@ -19458,7 +19622,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="C243">
         <v>683</v>
@@ -19532,7 +19696,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="C244">
         <v>839</v>
@@ -19606,7 +19770,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="C245">
         <v>817</v>
@@ -19680,7 +19844,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="C246">
         <v>786</v>
@@ -19754,7 +19918,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C247">
         <v>698</v>
@@ -19828,7 +19992,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="C248">
         <v>644</v>
@@ -19902,7 +20066,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="C249">
         <v>1147</v>
@@ -19976,7 +20140,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="C250">
         <v>970</v>
@@ -20050,7 +20214,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="C251">
         <v>555</v>
@@ -20124,7 +20288,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="C252">
         <v>929</v>
@@ -20198,7 +20362,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C253">
         <v>918</v>
@@ -20272,7 +20436,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="C254">
         <v>880</v>
@@ -20346,7 +20510,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="C255">
         <v>1041</v>
@@ -20420,7 +20584,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="C256">
         <v>917</v>
@@ -20494,7 +20658,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C257">
         <v>1135</v>
@@ -20568,7 +20732,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="C258">
         <v>1002</v>
@@ -20642,7 +20806,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="C259">
         <v>1167</v>
@@ -20716,7 +20880,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C260">
         <v>1029</v>
@@ -20790,7 +20954,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="C261">
         <v>1044</v>
@@ -20864,7 +21028,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="C262">
         <v>895</v>
@@ -20938,7 +21102,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="C263">
         <v>777</v>
@@ -21012,7 +21176,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="C264">
         <v>1057</v>
@@ -21086,7 +21250,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="C265">
         <v>972</v>
@@ -21160,7 +21324,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="C266">
         <v>1177</v>
@@ -21234,7 +21398,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="C267">
         <v>835</v>
@@ -21308,7 +21472,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="C268">
         <v>957</v>
@@ -21382,7 +21546,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="C269">
         <v>1044</v>
@@ -21456,7 +21620,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="C270">
         <v>1151</v>
@@ -21530,7 +21694,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="C271">
         <v>953</v>
@@ -21604,7 +21768,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="C272">
         <v>1035</v>
@@ -21678,7 +21842,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="C273">
         <v>659</v>
@@ -21752,7 +21916,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="C274">
         <v>793</v>
@@ -21826,7 +21990,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="C275">
         <v>846</v>
@@ -21900,7 +22064,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="C276">
         <v>708</v>
@@ -21974,7 +22138,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="C277">
         <v>586</v>
@@ -22048,7 +22212,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="C278">
         <v>510</v>
@@ -22122,7 +22286,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="C279">
         <v>376</v>
@@ -22196,7 +22360,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="C280">
         <v>755</v>
@@ -22270,7 +22434,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="C281">
         <v>533</v>
@@ -22344,7 +22508,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="C282">
         <v>1114</v>
@@ -22418,7 +22582,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="C283">
         <v>1093</v>
@@ -22492,7 +22656,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="C284">
         <v>635</v>
@@ -22566,7 +22730,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="C285">
         <v>956</v>
@@ -22640,7 +22804,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C286">
         <v>882</v>
@@ -22714,7 +22878,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="C287">
         <v>690</v>
@@ -22788,7 +22952,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="C288">
         <v>626</v>
@@ -22862,7 +23026,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C289">
         <v>1092</v>
@@ -22936,7 +23100,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="C290">
         <v>661</v>
@@ -23010,7 +23174,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="C291">
         <v>622</v>
@@ -23084,7 +23248,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="C292">
         <v>598</v>
@@ -23158,7 +23322,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="C293">
         <v>750</v>
@@ -23232,7 +23396,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C294">
         <v>895</v>
@@ -23306,7 +23470,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="C295">
         <v>467</v>
@@ -23380,7 +23544,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="C296">
         <v>1141</v>
@@ -23454,7 +23618,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C297">
         <v>370</v>
@@ -23528,7 +23692,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="C298">
         <v>663</v>
@@ -23602,7 +23766,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="C299">
         <v>691</v>
@@ -23676,7 +23840,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="C300">
         <v>704</v>
@@ -23750,7 +23914,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="C301">
         <v>1050</v>
@@ -23824,7 +23988,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="C302">
         <v>1071</v>
@@ -23898,7 +24062,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C303">
         <v>433</v>
@@ -23972,7 +24136,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C304">
         <v>791</v>
@@ -24046,7 +24210,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="C305">
         <v>1057</v>
@@ -24120,7 +24284,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C306">
         <v>839</v>
@@ -24194,7 +24358,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C307">
         <v>642</v>
@@ -24268,7 +24432,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="C308">
         <v>642</v>
@@ -24342,7 +24506,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="C309">
         <v>931</v>
@@ -24416,7 +24580,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C310">
         <v>378</v>
@@ -24490,7 +24654,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="C311">
         <v>995</v>
@@ -24564,7 +24728,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="C312">
         <v>896</v>
@@ -24638,7 +24802,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C313">
         <v>1046</v>
@@ -24712,7 +24876,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C314">
         <v>951</v>
@@ -24786,7 +24950,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C315">
         <v>703</v>
@@ -24860,7 +25024,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="C316">
         <v>686</v>
@@ -24934,7 +25098,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C317">
         <v>483</v>
@@ -25008,7 +25172,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C318">
         <v>1067</v>
@@ -25082,7 +25246,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="C319">
         <v>1060</v>
@@ -25156,7 +25320,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="C320">
         <v>712</v>
@@ -25230,7 +25394,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="C321">
         <v>653</v>
@@ -25304,7 +25468,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="C322">
         <v>475</v>
@@ -25378,7 +25542,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="C323">
         <v>856</v>
@@ -25452,7 +25616,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="C324">
         <v>703</v>
@@ -25526,7 +25690,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="C325">
         <v>581</v>
@@ -25600,7 +25764,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="C326">
         <v>735</v>
@@ -25674,7 +25838,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="C327">
         <v>853</v>
@@ -25748,7 +25912,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="C328">
         <v>366</v>
@@ -25822,7 +25986,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C329">
         <v>655</v>
@@ -25896,7 +26060,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="C330">
         <v>479</v>
@@ -25970,7 +26134,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="C331">
         <v>1040</v>
@@ -26044,7 +26208,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="C332">
         <v>893</v>
@@ -26118,7 +26282,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="C333">
         <v>943</v>
@@ -26192,7 +26356,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="C334">
         <v>513</v>
@@ -26266,7 +26430,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="C335">
         <v>943</v>
@@ -26340,7 +26504,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="C336">
         <v>682</v>
@@ -26414,7 +26578,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C337">
         <v>1016</v>
@@ -26488,7 +26652,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="C338">
         <v>772</v>
@@ -26562,7 +26726,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="C339">
         <v>1102</v>
@@ -26636,7 +26800,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="C340">
         <v>1094</v>
@@ -26710,7 +26874,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="C341">
         <v>1003</v>
@@ -26784,7 +26948,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="C342">
         <v>669</v>
@@ -26858,7 +27022,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C343">
         <v>647</v>
@@ -26932,7 +27096,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="C344">
         <v>1183</v>
@@ -27006,7 +27170,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="C345">
         <v>1025</v>
@@ -27080,7 +27244,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="C346">
         <v>1084</v>
@@ -27154,7 +27318,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="C347">
         <v>927</v>
@@ -27228,7 +27392,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="C348">
         <v>928</v>
@@ -27302,7 +27466,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="C349">
         <v>1097</v>
@@ -27376,7 +27540,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="C350">
         <v>1014</v>
@@ -27450,7 +27614,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="C351">
         <v>750</v>
@@ -27524,7 +27688,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="C352">
         <v>1160</v>
@@ -27598,7 +27762,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="C353">
         <v>705</v>
@@ -27672,7 +27836,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="C354">
         <v>708</v>
@@ -27746,7 +27910,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C355">
         <v>690</v>
@@ -27820,7 +27984,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="C356">
         <v>613</v>
@@ -27894,7 +28058,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="C357">
         <v>1045</v>
@@ -27968,7 +28132,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="C358">
         <v>989</v>
@@ -28042,7 +28206,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="C359">
         <v>1233</v>
@@ -28116,7 +28280,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="C360">
         <v>692</v>
@@ -28190,7 +28354,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="C361">
         <v>640</v>
@@ -28264,7 +28428,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="C362">
         <v>626</v>
@@ -28338,7 +28502,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="C363">
         <v>1170</v>
@@ -28412,7 +28576,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="C364">
         <v>1006</v>
@@ -28486,7 +28650,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="C365">
         <v>678</v>
@@ -28560,7 +28724,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="C366">
         <v>967</v>
@@ -28634,7 +28798,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="C367">
         <v>894</v>
@@ -28708,7 +28872,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="C368">
         <v>582</v>
@@ -28782,7 +28946,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="C369">
         <v>593</v>
@@ -28856,7 +29020,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="C370">
         <v>1194</v>
@@ -28930,7 +29094,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="C371">
         <v>995</v>
@@ -29004,7 +29168,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="C372">
         <v>786</v>
@@ -29078,7 +29242,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="C373">
         <v>874</v>
@@ -29152,7 +29316,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="C374">
         <v>987</v>
@@ -29226,7 +29390,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="C375">
         <v>787</v>
@@ -29300,7 +29464,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="C376">
         <v>893</v>
@@ -29374,7 +29538,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="C377">
         <v>416</v>
@@ -29448,7 +29612,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="C378">
         <v>835</v>
@@ -29522,7 +29686,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="C379">
         <v>522</v>
@@ -29596,7 +29760,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="C380">
         <v>705</v>
@@ -29670,7 +29834,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="C381">
         <v>499</v>
@@ -29744,7 +29908,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="C382">
         <v>831</v>
@@ -29818,7 +29982,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="C383">
         <v>877</v>
@@ -29892,7 +30056,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="C384">
         <v>1015</v>
@@ -29966,7 +30130,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="C385">
         <v>672</v>
@@ -30040,7 +30204,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="C386">
         <v>889</v>
@@ -30114,7 +30278,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="C387">
         <v>710</v>
@@ -30188,7 +30352,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="C388">
         <v>784</v>
@@ -30262,7 +30426,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="C389">
         <v>718</v>
@@ -30336,7 +30500,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="C390">
         <v>1188</v>
@@ -30410,7 +30574,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="C391">
         <v>825</v>
@@ -30484,7 +30648,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="C392">
         <v>503</v>
@@ -30558,7 +30722,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="C393">
         <v>851</v>
@@ -30632,7 +30796,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="C394">
         <v>652</v>
@@ -30706,7 +30870,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="C395">
         <v>662</v>
@@ -30780,7 +30944,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="C396">
         <v>628</v>
@@ -30854,7 +31018,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="C397">
         <v>1149</v>
@@ -30928,7 +31092,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C398">
         <v>620</v>
@@ -31002,7 +31166,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="C399">
         <v>555</v>
